--- a/Test Data/Regression/4689052_InHeaderImports02/UK_InHeader_ImportTb02.xlsx
+++ b/Test Data/Regression/4689052_InHeaderImports02/UK_InHeader_ImportTb02.xlsx
@@ -23,13 +23,13 @@
     <t>test Description</t>
   </si>
   <si>
-    <t>2222246_PWE01_1779771514911</t>
-  </si>
-  <si>
-    <t>2222246_PWE02_1779771514911</t>
-  </si>
-  <si>
-    <t>2222246_PWE03_1779771514911</t>
+    <t>2222246_PWE01_1780204192401</t>
+  </si>
+  <si>
+    <t>2222246_PWE02_1780204192401</t>
+  </si>
+  <si>
+    <t>2222246_PWE03_1780204192401</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>

--- a/Test Data/Regression/4689052_InHeaderImports02/UK_InHeader_ImportTb02.xlsx
+++ b/Test Data/Regression/4689052_InHeaderImports02/UK_InHeader_ImportTb02.xlsx
@@ -23,13 +23,13 @@
     <t>test Description</t>
   </si>
   <si>
-    <t>2222246_PWE01_1780204192401</t>
-  </si>
-  <si>
-    <t>2222246_PWE02_1780204192401</t>
-  </si>
-  <si>
-    <t>2222246_PWE03_1780204192401</t>
+    <t>2222246_PWE01_1780424268442</t>
+  </si>
+  <si>
+    <t>2222246_PWE02_1780424268442</t>
+  </si>
+  <si>
+    <t>2222246_PWE03_1780424268442</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>

--- a/Test Data/Regression/4689052_InHeaderImports02/UK_InHeader_ImportTb02.xlsx
+++ b/Test Data/Regression/4689052_InHeaderImports02/UK_InHeader_ImportTb02.xlsx
@@ -23,13 +23,13 @@
     <t>test Description</t>
   </si>
   <si>
-    <t>2222246_PWE01_1780424268442</t>
-  </si>
-  <si>
-    <t>2222246_PWE02_1780424268442</t>
-  </si>
-  <si>
-    <t>2222246_PWE03_1780424268442</t>
+    <t>2222246_PWE01_1780462542414</t>
+  </si>
+  <si>
+    <t>2222246_PWE02_1780462542414</t>
+  </si>
+  <si>
+    <t>2222246_PWE03_1780462542414</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>
